--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ניסים ניסן - מאושרת קאבר</v>
+        <v>נועם דדון - אני נשאר קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409941&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409990&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ניסים ניסן - מאושרת קאבר</v>
+        <v>נועם דדון - אני נשאר קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נדב קקון - ילדים של אלוקים קאבר</v>
+        <v>מיכאל כורש - אדם</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409940&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409989&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נדב קקון - ילדים של אלוקים קאבר</v>
+        <v>מיכאל כורש - אדם</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור כהן - חייל משמר הגבול קאבר</v>
+        <v>מאיר אלפי - ילד שלי קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409939&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409988&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור כהן - חייל משמר הגבול קאבר</v>
+        <v>מאיר אלפי - ילד שלי קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ליאור כהן - אבא קאבר</v>
+        <v>לידור יוסף - קחי אותי אלייך קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409938&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409987&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ליאור כהן - אבא קאבר</v>
+        <v>לידור יוסף - קחי אותי אלייך קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יקיר לנקרי - כל הכח קאבר</v>
+        <v>לידור יוסף - אתה הולך איתי קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409937&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409986&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יקיר לנקרי - כל הכח קאבר</v>
+        <v>לידור יוסף - אתה הולך איתי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ינון אלהרר - דמייני קאבר</v>
+        <v>לידור יוסף - אהיה לך בית קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409936&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409985&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ינון אלהרר - דמייני קאבר</v>
+        <v>לידור יוסף - אהיה לך בית קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>חנוך שובל - השיר שאת אהבת קאבר</v>
+        <v>יאיר יראי - ברגעים שאת הולכת &amp; נזכר בעיניה קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409935&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409984&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>חנוך שובל - השיר שאת אהבת קאבר</v>
+        <v>יאיר יראי - ברגעים שאת הולכת &amp; נזכר בעיניה קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אלרום יעקב - שוב חוזרת קאבר</v>
+        <v>דור שמר - מישל קאבר - גרסה עברית</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409934&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409983&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אלרום יעקב - שוב חוזרת קאבר</v>
+        <v>דור שמר - מישל קאבר - גרסה עברית</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלקנה אדרי &amp; שלום עברי - עומד בשער &amp; שמחות קטנות קאבר</v>
+        <v>אוראל מסיקה - אכבר גבר &amp; צונאמי קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409933&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409982&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,50 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלקנה אדרי &amp; שלום עברי - עומד בשער &amp; שמחות קטנות קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אלון מיכאל - מלון בהוואי קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409932&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אלון מיכאל - מלון בהוואי קאבר</v>
+        <v>אוראל מסיקה - אכבר גבר &amp; צונאמי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>